--- a/data/data_monitoreo_malingas.xlsx
+++ b/data/data_monitoreo_malingas.xlsx
@@ -447,77 +447,77 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>208</v>
+        <v>255</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>URRIOLA ARISMENDIZ INGRID MARYURI</t>
+          <t>ATOCHE PALACIOS LUIS ANGEL</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>197</v>
+        <v>247</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MANUEL LEUNARDO PRADO BAILON</t>
+          <t>MARYURI OJEDA VALLE</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>193</v>
+        <v>238</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CORDOVA CARMEN ANGIE NATALLY</t>
+          <t>MANUEL LEUNARDO PRADO BAILON</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>184</v>
+        <v>237</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MARYURI OJEDA VALLE</t>
+          <t>URRIOLA ARISMENDIZ INGRID MARYURI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>184</v>
+        <v>229</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ATOCHE PALACIOS LUIS ANGEL</t>
+          <t>ALAMA NIMA CLARITZA MABEL</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>182</v>
+        <v>224</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ALAMA NIMA CLARITZA MABEL</t>
+          <t>VEGA ROBLEDO FERNANDO ERNESTO</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>179</v>
+        <v>207</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AGURTO ORDINOLA LISBET JAQUELIN</t>
+          <t>CORDOVA CARMEN ANGIE NATALLY</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>174</v>
+        <v>205</v>
       </c>
     </row>
     <row r="10">
@@ -527,37 +527,37 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>169</v>
+        <v>199</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>VEGA ROBLEDO FERNANDO ERNESTO</t>
+          <t>AGURTO ORDINOLA LISBET JAQUELIN</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>159</v>
+        <v>182</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>JUAREZ CARMEN PIERRE ALEXANDER</t>
+          <t>ROMAN GALECIO MARITZA DEL PILAR</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>157</v>
+        <v>180</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ROMAN GALECIO MARITZA DEL PILAR</t>
+          <t>JUAREZ CARMEN PIERRE ALEXANDER</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>150</v>
+        <v>178</v>
       </c>
     </row>
     <row r="14">
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>143</v>
+        <v>171</v>
       </c>
     </row>
     <row r="15">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>120</v>
+        <v>153</v>
       </c>
     </row>
     <row r="16">

--- a/data/data_monitoreo_malingas.xlsx
+++ b/data/data_monitoreo_malingas.xlsx
@@ -443,21 +443,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ALBIRENA GARCIA ANGEELO ALONSO</t>
+          <t>ATOCHE PALACIOS LUIS ANGEL</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>255</v>
+        <v>269</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ATOCHE PALACIOS LUIS ANGEL</t>
+          <t>ALBIRENA GARCIA ANGEELO ALONSO</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>247</v>
+        <v>255</v>
       </c>
     </row>
     <row r="4">
@@ -467,17 +467,17 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>238</v>
+        <v>248</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MANUEL LEUNARDO PRADO BAILON</t>
+          <t>ALAMA NIMA CLARITZA MABEL</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>237</v>
+        <v>247</v>
       </c>
     </row>
     <row r="6">
@@ -487,67 +487,67 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>229</v>
+        <v>246</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ALAMA NIMA CLARITZA MABEL</t>
+          <t>MANUEL LEUNARDO PRADO BAILON</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>224</v>
+        <v>244</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>VEGA ROBLEDO FERNANDO ERNESTO</t>
+          <t>CORDOVA CARMEN ANGIE NATALLY</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>207</v>
+        <v>237</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CORDOVA CARMEN ANGIE NATALLY</t>
+          <t>VEGA ROBLEDO FERNANDO ERNESTO</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>205</v>
+        <v>217</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>RUIDIAS FRIAS MELISSA VICTORIA</t>
+          <t>AGURTO ORDINOLA LISBET JAQUELIN</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>199</v>
+        <v>215</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AGURTO ORDINOLA LISBET JAQUELIN</t>
+          <t>ROMAN GALECIO MARITZA DEL PILAR</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>182</v>
+        <v>214</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ROMAN GALECIO MARITZA DEL PILAR</t>
+          <t>RUIDIAS FRIAS MELISSA VICTORIA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>180</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>178</v>
+        <v>194</v>
       </c>
     </row>
     <row r="14">
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>171</v>
+        <v>180</v>
       </c>
     </row>
     <row r="15">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>153</v>
+        <v>179</v>
       </c>
     </row>
     <row r="16">

--- a/data/data_monitoreo_malingas.xlsx
+++ b/data/data_monitoreo_malingas.xlsx
@@ -447,27 +447,27 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>269</v>
+        <v>286</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ALBIRENA GARCIA ANGEELO ALONSO</t>
+          <t>MARYURI OJEDA VALLE</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>255</v>
+        <v>275</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MARYURI OJEDA VALLE</t>
+          <t>ALBIRENA GARCIA ANGEELO ALONSO</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>248</v>
+        <v>273</v>
       </c>
     </row>
     <row r="5">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>247</v>
+        <v>260</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>246</v>
+        <v>259</v>
       </c>
     </row>
     <row r="7">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>244</v>
+        <v>255</v>
       </c>
     </row>
     <row r="8">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>237</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>217</v>
+        <v>234</v>
       </c>
     </row>
     <row r="10">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>215</v>
+        <v>227</v>
       </c>
     </row>
     <row r="11">
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>214</v>
+        <v>224</v>
       </c>
     </row>
     <row r="12">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>207</v>
+        <v>221</v>
       </c>
     </row>
     <row r="13">
@@ -557,27 +557,27 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>194</v>
+        <v>213</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BERNAOLA CARMEN ZUMIKO YASHURY</t>
+          <t>CARREÑO PALACIOS KATHERINE DE LOS MILAGROS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>180</v>
+        <v>198</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CARREÑO PALACIOS KATHERINE DE LOS MILAGROS</t>
+          <t>BERNAOLA CARMEN ZUMIKO YASHURY</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>179</v>
+        <v>197</v>
       </c>
     </row>
     <row r="16">

--- a/data/data_monitoreo_malingas.xlsx
+++ b/data/data_monitoreo_malingas.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="4">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="7">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="8">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="9">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="10">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="11">
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="12">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="13">
@@ -557,27 +557,27 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>213</v>
+        <v>217</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CARREÑO PALACIOS KATHERINE DE LOS MILAGROS</t>
+          <t>BERNAOLA CARMEN ZUMIKO YASHURY</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BERNAOLA CARMEN ZUMIKO YASHURY</t>
+          <t>CARREÑO PALACIOS KATHERINE DE LOS MILAGROS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="16">

--- a/data/data_monitoreo_malingas.xlsx
+++ b/data/data_monitoreo_malingas.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>290</v>
+        <v>297</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>279</v>
+        <v>285</v>
       </c>
     </row>
     <row r="4">
@@ -467,27 +467,27 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>273</v>
+        <v>279</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ALAMA NIMA CLARITZA MABEL</t>
+          <t>URRIOLA ARISMENDIZ INGRID MARYURI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>262</v>
+        <v>272</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>URRIOLA ARISMENDIZ INGRID MARYURI</t>
+          <t>ALAMA NIMA CLARITZA MABEL</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>261</v>
+        <v>266</v>
       </c>
     </row>
     <row r="7">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>257</v>
+        <v>261</v>
       </c>
     </row>
     <row r="8">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>248</v>
+        <v>251</v>
       </c>
     </row>
     <row r="9">
@@ -517,27 +517,27 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>236</v>
+        <v>240</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AGURTO ORDINOLA LISBET JAQUELIN</t>
+          <t>ROMAN GALECIO MARITZA DEL PILAR</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>229</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ROMAN GALECIO MARITZA DEL PILAR</t>
+          <t>AGURTO ORDINOLA LISBET JAQUELIN</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>227</v>
+        <v>236</v>
       </c>
     </row>
     <row r="12">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="13">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="14">
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="15">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>198</v>
+        <v>204</v>
       </c>
     </row>
     <row r="16">

--- a/data/data_monitoreo_malingas.xlsx
+++ b/data/data_monitoreo_malingas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>285</v>
+        <v>290</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="5">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="8">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="10">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11">
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="12">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="13">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="14">
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="15">
@@ -583,10 +583,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>47356835</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>PIÑIN MACHUCA GIANCARLO</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="B17" t="n">
         <v>1</v>
       </c>
     </row>

--- a/data/data_monitoreo_malingas.xlsx
+++ b/data/data_monitoreo_malingas.xlsx
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="8">
@@ -523,17 +523,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ROMAN GALECIO MARITZA DEL PILAR</t>
+          <t>AGURTO ORDINOLA LISBET JAQUELIN</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AGURTO ORDINOLA LISBET JAQUELIN</t>
+          <t>ROMAN GALECIO MARITZA DEL PILAR</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>210</v>
+        <v>215</v>
       </c>
     </row>
     <row r="15">
